--- a/SupplementaryTables/ssrm_suppTables.xlsx
+++ b/SupplementaryTables/ssrm_suppTables.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365.sharepoint.com/sites/A8-VT-Grembi_Lab/Shared Documents/01_Projects/SSRB_manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ehd5113/human-gut-ssrm-capscan/SupplementaryTables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E14E7D95-CE5A-4011-861B-E900C582BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CA07A2-6D62-144C-9B21-489D72FBCA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43840" yWindow="10900" windowWidth="27640" windowHeight="16740" firstSheet="2" activeTab="1" xr2:uid="{C171AF22-812F-0C42-B48C-B2ABBD8475A5}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29100" windowHeight="16840" activeTab="3" xr2:uid="{C171AF22-812F-0C42-B48C-B2ABBD8475A5}"/>
   </bookViews>
   <sheets>
     <sheet name="SuppTable1" sheetId="4" r:id="rId1"/>
-    <sheet name="SuppTable2" sheetId="1" r:id="rId2"/>
-    <sheet name="SuppTable3" sheetId="2" r:id="rId3"/>
+    <sheet name="SuppTable2" sheetId="2" r:id="rId2"/>
+    <sheet name="SuppTable3" sheetId="1" r:id="rId3"/>
+    <sheet name="SuppTable4" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="395">
   <si>
     <t>FILTER SETS FOR 2022</t>
   </si>
@@ -1049,15 +1050,290 @@
   <si>
     <t>Remaining 18 clusters have only the rep species included in them</t>
   </si>
+  <si>
+    <t>Sample SSRM prevalence</t>
+  </si>
+  <si>
+    <t>Sequencing depth notes</t>
+  </si>
+  <si>
+    <t>Reads to Gnt calculation</t>
+  </si>
+  <si>
+    <t>Depth in Gnt, pre- or post-"QC" (trim, human-reads removal, etc.)</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Additional notes</t>
+  </si>
+  <si>
+    <t>"After sequencing and before biocomputing quality control, the sequencing depth (mean ±s.d.) for DNA was 3.8 ± 1.6 giganucleotides (Gnt). After quality control, it was 1.8 ± 0.7 Gnt"</t>
+  </si>
+  <si>
+    <t>3.8 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41564-017-0096-0</t>
+  </si>
+  <si>
+    <t>"Metagenomic libraries were sequenced on the Illumina HiSeq 2500 platform, targeting ~2.5 Gb of sequence per
+sample with 101 bp, paired-end reads." ; document S1</t>
+  </si>
+  <si>
+    <t>2.5 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cell.2016.04.007</t>
+  </si>
+  <si>
+    <t>"One paired-end library with insert size of 350 bp for each sample was built and sequenced with 100 bp read length from each end. Adaptor contamination, low-quality reads, and host contaminating reads were removed from the raw sequencing reads sets. On average 39.9 million high-quality reads per sample were generated for further analyses. The proportion of high-quality reads among all raw reads from each sample was 86.7% on average." 46.0 million pre-QC accorfing to Table S2</t>
+  </si>
+  <si>
+    <t>9.2 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.chom.2015.04.004</t>
+  </si>
+  <si>
+    <t>"Subsequently, samples were submitted for paired-end 150-bp sequencing using the Illumina HiSeq 2500 platform at GTAC.... In total, 401 samples across 10 HiSeq lanes were sequenced to sufficient depth (1 million reads) for microbiome and resistome analyses. Technical replicates (two or three) of each fecal metagenomic DNA sample were individually barcoded and pooled for sequencing, and total reads per biological sample were used for analysis." According to Table S1, average of 9.16 million reads per sample ("Shotgun:NumSeq_Total", includes about 15 samples not in our dataset, but good approximation) so divide this by 2.5 to get the average for an individual replicate.</t>
+  </si>
+  <si>
+    <t>1.1 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nmicrobiol.2016.24</t>
+  </si>
+  <si>
+    <t>supplemental: "obtain around 20 million PE
+reads. The reads length for each end is 75bp-90bp (75bp and 90bp read length in
+stage I samples; 90bp read length for stage II samples). High quality reads were
+extracted by filtering low quality reads with ‘N’ base, adapter contamination or
+human DNA contamination from the Illumina raw data. On average, the proportion
+of high quality reads in all samples was about 98.1%, and the actual insert size of our
+PE library ranges from 313bp to 381bp."</t>
+  </si>
+  <si>
+    <t>3.3 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nature11450</t>
+  </si>
+  <si>
+    <t>"Finally, we generated 26.0 million–186.1 million high-quality reads for the 292 samples, with an average of 68.2 million high-quality reads. Sequencing read length of the first batch of 15 samples was 44 bp, the second batch was 75 bp, and the third batch was 75 bp and 90 bp....An average of 34.1 million paired-end reads were produced for each sample and, after removing human contamination"</t>
+  </si>
+  <si>
+    <t>5.1 (pre-QC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1038/nature12506
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table S26 average over 257 samples </t>
+  </si>
+  <si>
+    <t>5.5 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nm.4358</t>
+  </si>
+  <si>
+    <t>Average taken from the samples we have extracted from supplementary table 1</t>
+  </si>
+  <si>
+    <t>11.9 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nbt.2942</t>
+  </si>
+  <si>
+    <t>"All were subjected to Illumina deep sequencing resulting in 4.5 Gb sequence per sample on average, and a total of 23.2 billion high-quality sequencing reads with an average length of 77 bp." Using Supplementary Data 1, Raw bases is 4.9 Gnt across the samples we have.</t>
+  </si>
+  <si>
+    <t>4.9 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nbt.2939</t>
+  </si>
+  <si>
+    <t>"Paired-end metagenomic sequencing was done on the Illumina platform (insert size, 350 bp; read length, 100 bp)"; no sequencing stats were found</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nm.3914</t>
+  </si>
+  <si>
+    <t>varies based on sequencing type, supplemental</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/dnares/dsw002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study could have a slightly higher prevalence because some of the samples appear to be single-end reads (e.g. a subject might have samples from 4 data points but each of those samples are sequenced in different manners). The S1 table does not say which timepoint corresponds to which sequencing method. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Paired-end metagenomic sequencing was performed on the Illumina platform (insert size 350 bp, read length 100 bp)"; supp. Dataset 2 average raw reads count: 5,638,188,181 </t>
+  </si>
+  <si>
+    <t>5.6 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/ncomms7528</t>
+  </si>
+  <si>
+    <t>presented as if it is reads but it has to be bases, based on what was uploaded to the SRA</t>
+  </si>
+  <si>
+    <t>"Illumina Hiseq 4000 platform with 150 bp paired-end read length" average of clean bases from Table S3</t>
+  </si>
+  <si>
+    <t>6.1 (post-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/19490976.2019.1700754</t>
+  </si>
+  <si>
+    <t>calculation doesn’t include all of the samples</t>
+  </si>
+  <si>
+    <t>from table S2: average raw reads cases (60496561) and controls (60162577)</t>
+  </si>
+  <si>
+    <t>12.1 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1136/gutjnl-2015-309800</t>
+  </si>
+  <si>
+    <t>assuming length of 100 based on uploaded SRA calculations (bases/spots)</t>
+  </si>
+  <si>
+    <t>"Samples were pooled at equal nanomolar concentration and either 125- or 150-base paired-end reads were generated on the Illumina NextSeq and HiSeq instruments." additional file 1: mWGS raw reads: 26,202,286 (± 6,757,859)</t>
+  </si>
+  <si>
+    <t>7.9 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s40168-017-0320-4</t>
+  </si>
+  <si>
+    <t>"The samples were sequenced with a 100-bp read length for paired-end sequences at the Genomics Core Facility, European Molecular Biology Laboratory, Heidelberg, Germany with a targeted sequencing depth of 5 Gbp."</t>
+  </si>
+  <si>
+    <t>5 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1371/journal.pone.0155362</t>
+  </si>
+  <si>
+    <t>This depth seems low compared to what is reported on NCBI</t>
+  </si>
+  <si>
+    <t>supplementary methods: "...high-throughput sequencing to obtain around 30 million
+PE reads with a of length 2x100bp."</t>
+  </si>
+  <si>
+    <t>6 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/srep22525</t>
+  </si>
+  <si>
+    <t>very likely this paper</t>
+  </si>
+  <si>
+    <t>"Sequencing was done with 2x100 nucleotides (paired-end sequencing) ... Samples were sequenced with a sequencing depth of 10.9 million reads per paired-end sequencing file (s = 6.3 million)."</t>
+  </si>
+  <si>
+    <t>2.2 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1371/journal.pone.0149564</t>
+  </si>
+  <si>
+    <t>10.8 (pre-QC)</t>
+  </si>
+  <si>
+    <t>likely this paper</t>
+  </si>
+  <si>
+    <t>Supplemental: "For each library, eight
+samples were pooled in order to achieve around 15 million reads/lane….100 bp paired-end read sequencing"</t>
+  </si>
+  <si>
+    <t>3 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.chom.2016.09.001</t>
+  </si>
+  <si>
+    <t>NCBI uploads suggest it is 15 million reads per sample</t>
+  </si>
+  <si>
+    <t>"shotgun sequenced (paired end)"; raw bases average 7,771,222,509 and average read length 100 (see additional file 3)</t>
+  </si>
+  <si>
+    <t>7.8 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s13073-017-0428-y</t>
+  </si>
+  <si>
+    <t>Hard to tell how they are reporting the stats because they don't clearly match NCBI uploads</t>
+  </si>
+  <si>
+    <t>"Samples with fewer than 1 million total reads (paired and unpaired) were excluded from further analysis." Supplemental only contains read info for assemblies</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nature17672</t>
+  </si>
+  <si>
+    <t>Supplementary materials: "Sequencing
+libraries were paired-end sequenced (100bp read length) to a targeted raw sequencing
+depth of 7 Gbp"</t>
+  </si>
+  <si>
+    <t>7 (pre-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1126/science.aad8852</t>
+  </si>
+  <si>
+    <t>"DNA was sequenced with 101 bp (per paired end) on a HiSeq2000 system (Illumina) by BGI." and from supplementary table 3: "metagenomic data (after quality filtering)*": mean 3,850 Mbp ("*statistics on metagenomic data include only samples for which coupled metatranscriptomic and metaproteomic data were obtained.")</t>
+  </si>
+  <si>
+    <t>3.9 (post-QC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1038/nmicrobiol.2016.180
+</t>
+  </si>
+  <si>
+    <t>"Metagenomic libraries were sequenced on the Illumina HiSeq 2500 platform, targeting ~5.0 Gb of sequence per sample with 101 bp, paired-end reads."</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1097/MIB.0000000000000893</t>
+  </si>
+  <si>
+    <t>"total #bp in trimmed reads"; average taken from 48 samples in table S2 (two in ncbi but not in the table)</t>
+  </si>
+  <si>
+    <t>2.9 (post-QC)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7554/eLife.05477</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1158,8 +1434,28 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1178,8 +1474,26 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1187,13 +1501,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1236,18 +1606,112 @@
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{EACDC065-BB07-0B49-B138-CE0187A46AC0}"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
@@ -1889,24 +2353,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z59"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.875" style="12" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="12"/>
+    <col min="1" max="1" width="19.83203125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="12"/>
     <col min="3" max="3" width="20" style="12" customWidth="1"/>
-    <col min="4" max="4" width="26.375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="12" customWidth="1"/>
     <col min="6" max="7" width="24" style="12" customWidth="1"/>
-    <col min="8" max="8" width="54.625" style="12" customWidth="1"/>
-    <col min="9" max="16384" width="12.625" style="12"/>
+    <col min="8" max="8" width="54.6640625" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="12.6640625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
@@ -1932,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>9</v>
       </c>
@@ -1972,7 +2436,7 @@
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>12</v>
       </c>
@@ -1994,14 +2458,14 @@
       <c r="G4" s="19"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="24">
         <v>44593</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="17" t="s">
@@ -2015,19 +2479,19 @@
       </c>
       <c r="G5" s="19"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="19"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="24">
@@ -2047,175 +2511,175 @@
       </c>
       <c r="G7" s="19"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="23" t="s">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="19"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="19"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="19"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="19"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="19"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
       <c r="G16" s="19"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="19"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="19"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
       <c r="D20" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
       <c r="D21" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="19"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A23" s="23" t="s">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="24">
@@ -2235,87 +2699,87 @@
       </c>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="23" t="s">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
       <c r="D26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="19"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
       <c r="D28" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
       <c r="G28" s="19"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
       <c r="D29" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
       <c r="G29" s="19"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
       <c r="D30" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
       <c r="G30" s="19"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
         <v>45</v>
       </c>
       <c r="B31" s="24">
@@ -2327,40 +2791,40 @@
       <c r="D31" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="22">
         <v>462</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="22">
         <v>255</v>
       </c>
       <c r="G31" s="17"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="23" t="s">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A33" s="26"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
       <c r="D33" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="22" t="s">
         <v>48</v>
       </c>
       <c r="B34" s="24">
@@ -2372,40 +2836,40 @@
       <c r="D34" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="22">
         <v>173</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="22">
         <v>115</v>
       </c>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="23" t="s">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
       <c r="G35" s="17"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
       <c r="D36" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
       <c r="G36" s="17"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A37" s="23" t="s">
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="22" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="24">
@@ -2425,76 +2889,76 @@
       </c>
       <c r="G37" s="19"/>
     </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="23" t="s">
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
       <c r="G38" s="19"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
       <c r="D39" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
       <c r="G39" s="19"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
       <c r="D40" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
       <c r="G40" s="19"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
       <c r="G41" s="19"/>
     </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
       <c r="D42" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
       <c r="G42" s="19"/>
     </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
       <c r="D43" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A44" s="23" t="s">
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="22" t="s">
         <v>57</v>
       </c>
       <c r="B44" s="24">
@@ -2514,109 +2978,109 @@
       </c>
       <c r="G44" s="19"/>
     </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="23" t="s">
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
       <c r="G45" s="19"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
       <c r="D46" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
       <c r="G46" s="19"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
       <c r="D47" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
       <c r="G47" s="19"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
       <c r="D48" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="19"/>
     </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
       <c r="D49" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
       <c r="G49" s="19"/>
     </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
       <c r="D50" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="19"/>
     </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
       <c r="G51" s="19"/>
     </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A52" s="26"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A53" s="26"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
       <c r="G53" s="19"/>
     </row>
-    <row r="54" spans="1:7" ht="14.1">
-      <c r="A54" s="23" t="s">
+    <row r="54" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A54" s="22" t="s">
         <v>67</v>
       </c>
       <c r="B54" s="24">
@@ -2628,40 +3092,40 @@
       <c r="D54" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="22">
         <v>796</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="22">
         <v>637</v>
       </c>
       <c r="G54" s="17"/>
     </row>
-    <row r="55" spans="1:7" ht="14.1">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="23" t="s">
+    <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="22" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="17"/>
     </row>
-    <row r="56" spans="1:7" ht="14.1">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
+    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
       <c r="D56" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
       <c r="G56" s="17"/>
     </row>
-    <row r="57" spans="1:7" ht="14.1">
-      <c r="A57" s="23" t="s">
+    <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A57" s="22" t="s">
         <v>70</v>
       </c>
       <c r="B57" s="24">
@@ -2673,34 +3137,34 @@
       <c r="D57" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="23">
+      <c r="E57" s="22">
         <v>58</v>
       </c>
-      <c r="F57" s="23">
+      <c r="F57" s="22">
         <v>58</v>
       </c>
       <c r="G57" s="17"/>
     </row>
-    <row r="58" spans="1:7" ht="14.1">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26"/>
+    <row r="58" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
       <c r="C58" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
       <c r="G58" s="17"/>
     </row>
-    <row r="59" spans="1:7" ht="14.1">
-      <c r="A59" s="22" t="s">
+    <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.2">
+      <c r="A59" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
       <c r="E59" s="19">
         <f>SUM(E4:E56)</f>
         <v>111914</v>
@@ -2715,70 +3179,442 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A44:A53"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="E44:E53"/>
+    <mergeCell ref="F44:F53"/>
+    <mergeCell ref="C45:C53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="E37:E43"/>
+    <mergeCell ref="F37:F43"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="E23:E30"/>
+    <mergeCell ref="F23:F30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="A7:A22"/>
     <mergeCell ref="B7:B22"/>
     <mergeCell ref="E7:E22"/>
     <mergeCell ref="F7:F22"/>
     <mergeCell ref="C8:C22"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="E23:E30"/>
-    <mergeCell ref="F23:F30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="A37:A43"/>
-    <mergeCell ref="B37:B43"/>
-    <mergeCell ref="E37:E43"/>
-    <mergeCell ref="F37:F43"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="E44:E53"/>
-    <mergeCell ref="F44:F53"/>
-    <mergeCell ref="C45:C53"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="A59:D59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3F2F6F-D8F7-40A9-8B90-1693E8CE9DF5}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2" s="21">
+        <v>99.844999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="21">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B4" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" s="21">
+        <v>99.578999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="21">
+        <v>99.578999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="21">
+        <v>99.950999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B7" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" s="21">
+        <v>92.688999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D8" s="21">
+        <v>92.738</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="21">
+        <v>99.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" s="21">
+        <v>98.506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="21">
+        <v>97.63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="21">
+        <v>92.272000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="21">
+        <v>91.841999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" s="21">
+        <v>91.087000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" s="21">
+        <v>90.828999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="D16" s="21">
+        <v>96.856999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B17" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D17" s="21">
+        <v>92.022999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" s="21">
+        <v>91.578999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B19" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D19" s="21">
+        <v>90.828999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" s="21">
+        <v>90.478999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B21" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="21">
+        <v>91.757000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B22" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="21">
+        <v>91.477999999999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B23" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D23" s="21">
+        <v>90.674999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B24" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" s="21">
+        <v>90.366</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B25" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D25" s="21">
+        <v>94.632000000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B26" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D26" s="21">
+        <v>92.89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B27" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27" s="21">
+        <v>92.588999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B28" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="21">
+        <v>92.841999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B29" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" s="21">
+        <v>92.421000000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.25">
+      <c r="B30" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" s="21">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555EE2FB-F52D-C246-B6FB-0576A62D6478}">
   <dimension ref="A1:F72"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="41.1" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="41" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="70.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="70.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="53.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="41.1" customHeight="1">
+    <row r="1" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>73</v>
       </c>
@@ -2798,7 +3634,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="41.1" customHeight="1">
+    <row r="2" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>79</v>
       </c>
@@ -2818,7 +3654,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="41.1" customHeight="1">
+    <row r="3" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>84</v>
       </c>
@@ -2838,7 +3674,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="41.1" customHeight="1">
+    <row r="4" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>89</v>
       </c>
@@ -2858,7 +3694,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="41.1" customHeight="1">
+    <row r="5" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>92</v>
       </c>
@@ -2878,7 +3714,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="41.1" customHeight="1">
+    <row r="6" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
@@ -2898,7 +3734,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="41.1" customHeight="1">
+    <row r="7" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>99</v>
       </c>
@@ -2918,7 +3754,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="41.1" customHeight="1">
+    <row r="8" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>103</v>
       </c>
@@ -2938,7 +3774,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="41.1" customHeight="1">
+    <row r="9" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>105</v>
       </c>
@@ -2958,7 +3794,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="41.1" customHeight="1">
+    <row r="10" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>109</v>
       </c>
@@ -2978,7 +3814,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="41.1" customHeight="1">
+    <row r="11" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>112</v>
       </c>
@@ -2998,7 +3834,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="41.1" customHeight="1">
+    <row r="12" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>115</v>
       </c>
@@ -3018,7 +3854,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="41.1" customHeight="1">
+    <row r="13" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>118</v>
       </c>
@@ -3038,7 +3874,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="41.1" customHeight="1">
+    <row r="14" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>120</v>
       </c>
@@ -3058,7 +3894,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="41.1" customHeight="1">
+    <row r="15" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>124</v>
       </c>
@@ -3078,7 +3914,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="41.1" customHeight="1">
+    <row r="16" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>127</v>
       </c>
@@ -3098,7 +3934,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="41.1" customHeight="1">
+    <row r="17" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>129</v>
       </c>
@@ -3118,7 +3954,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="41.1" customHeight="1">
+    <row r="18" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>131</v>
       </c>
@@ -3138,7 +3974,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="41.1" customHeight="1">
+    <row r="19" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>133</v>
       </c>
@@ -3158,7 +3994,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="41.1" customHeight="1">
+    <row r="20" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>136</v>
       </c>
@@ -3178,7 +4014,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="41.1" customHeight="1">
+    <row r="21" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>139</v>
       </c>
@@ -3198,7 +4034,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="41.1" customHeight="1">
+    <row r="22" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>142</v>
       </c>
@@ -3218,7 +4054,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="41.1" customHeight="1">
+    <row r="23" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>144</v>
       </c>
@@ -3238,7 +4074,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="41.1" customHeight="1">
+    <row r="24" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>146</v>
       </c>
@@ -3258,7 +4094,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="41.1" customHeight="1">
+    <row r="25" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>149</v>
       </c>
@@ -3278,7 +4114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="41.1" customHeight="1">
+    <row r="26" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>153</v>
       </c>
@@ -3298,7 +4134,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="41.1" customHeight="1">
+    <row r="27" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>157</v>
       </c>
@@ -3318,7 +4154,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="41.1" customHeight="1">
+    <row r="28" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>161</v>
       </c>
@@ -3338,7 +4174,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="41.1" customHeight="1">
+    <row r="29" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>164</v>
       </c>
@@ -3358,7 +4194,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="41.1" customHeight="1">
+    <row r="30" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>167</v>
       </c>
@@ -3378,7 +4214,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="41.1" customHeight="1">
+    <row r="31" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3398,7 +4234,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="41.1" customHeight="1">
+    <row r="32" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>174</v>
       </c>
@@ -3418,7 +4254,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="41.1" customHeight="1">
+    <row r="33" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>176</v>
       </c>
@@ -3438,7 +4274,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="41.1" customHeight="1">
+    <row r="34" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>178</v>
       </c>
@@ -3458,7 +4294,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="41.1" customHeight="1">
+    <row r="35" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>180</v>
       </c>
@@ -3478,7 +4314,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="41.1" customHeight="1">
+    <row r="36" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>182</v>
       </c>
@@ -3498,7 +4334,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="41.1" customHeight="1">
+    <row r="37" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>186</v>
       </c>
@@ -3518,7 +4354,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="41.1" customHeight="1">
+    <row r="38" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>190</v>
       </c>
@@ -3538,7 +4374,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="41.1" customHeight="1">
+    <row r="39" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>193</v>
       </c>
@@ -3558,7 +4394,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="41.1" customHeight="1">
+    <row r="40" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>196</v>
       </c>
@@ -3578,7 +4414,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="41.1" customHeight="1">
+    <row r="41" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>199</v>
       </c>
@@ -3598,7 +4434,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="41.1" customHeight="1">
+    <row r="42" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>202</v>
       </c>
@@ -3618,7 +4454,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="41.1" customHeight="1">
+    <row r="43" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>205</v>
       </c>
@@ -3638,7 +4474,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="41.1" customHeight="1">
+    <row r="44" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>207</v>
       </c>
@@ -3658,7 +4494,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="41.1" customHeight="1">
+    <row r="45" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
         <v>211</v>
       </c>
@@ -3678,7 +4514,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="41.1" customHeight="1">
+    <row r="46" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>214</v>
       </c>
@@ -3698,7 +4534,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="41.1" customHeight="1">
+    <row r="47" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>217</v>
       </c>
@@ -3718,7 +4554,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="41.1" customHeight="1">
+    <row r="48" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>220</v>
       </c>
@@ -3738,7 +4574,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="41.1" customHeight="1">
+    <row r="49" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>222</v>
       </c>
@@ -3758,7 +4594,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="41.1" customHeight="1">
+    <row r="50" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>225</v>
       </c>
@@ -3778,7 +4614,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="41.1" customHeight="1">
+    <row r="51" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>229</v>
       </c>
@@ -3798,7 +4634,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="41.1" customHeight="1">
+    <row r="52" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>231</v>
       </c>
@@ -3818,7 +4654,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="41.1" customHeight="1">
+    <row r="53" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>151</v>
       </c>
@@ -3838,7 +4674,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="41.1" customHeight="1">
+    <row r="54" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>236</v>
       </c>
@@ -3858,7 +4694,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="41.1" customHeight="1">
+    <row r="55" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>239</v>
       </c>
@@ -3878,7 +4714,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="41.1" customHeight="1">
+    <row r="56" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>241</v>
       </c>
@@ -3898,7 +4734,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="41.1" customHeight="1">
+    <row r="57" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>243</v>
       </c>
@@ -3918,7 +4754,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="41.1" customHeight="1">
+    <row r="58" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>245</v>
       </c>
@@ -3938,7 +4774,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="41.1" customHeight="1">
+    <row r="59" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>248</v>
       </c>
@@ -3958,7 +4794,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="41.1" customHeight="1">
+    <row r="60" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>151</v>
       </c>
@@ -3978,7 +4814,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="41.1" customHeight="1">
+    <row r="61" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>251</v>
       </c>
@@ -3998,7 +4834,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="41.1" customHeight="1">
+    <row r="62" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>253</v>
       </c>
@@ -4018,7 +4854,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="41.1" customHeight="1">
+    <row r="63" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>255</v>
       </c>
@@ -4038,7 +4874,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="41.1" customHeight="1">
+    <row r="64" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>257</v>
       </c>
@@ -4058,7 +4894,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="41.1" customHeight="1">
+    <row r="65" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>260</v>
       </c>
@@ -4078,7 +4914,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="41.1" customHeight="1">
+    <row r="66" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>263</v>
       </c>
@@ -4098,7 +4934,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="41.1" customHeight="1">
+    <row r="67" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>151</v>
       </c>
@@ -4118,7 +4954,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="41.1" customHeight="1">
+    <row r="68" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>268</v>
       </c>
@@ -4138,7 +4974,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="41.1" customHeight="1">
+    <row r="69" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>271</v>
       </c>
@@ -4158,7 +4994,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="41.1" customHeight="1">
+    <row r="70" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>274</v>
       </c>
@@ -4178,7 +5014,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="41.1" customHeight="1">
+    <row r="71" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>276</v>
       </c>
@@ -4198,7 +5034,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="41.1" customHeight="1">
+    <row r="72" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>278</v>
       </c>
@@ -4226,372 +5062,1100 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3F2F6F-D8F7-40A9-8B90-1693E8CE9DF5}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.95"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCAABBC-8D5F-A842-A908-3A3D7EADED5B}">
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="15.875" customWidth="1"/>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
-    <col min="4" max="4" width="23.375" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="27.6640625" customWidth="1"/>
+    <col min="8" max="10" width="25.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="17.100000000000001">
-      <c r="A2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" s="21">
-        <v>99.844999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="17.100000000000001">
-      <c r="A3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="21">
+    <row r="1" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="6">
+        <v>915</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="31">
+        <v>9.4E-2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="32">
+        <v>737</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="34">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>318</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="L3" s="36"/>
+    </row>
+    <row r="4" spans="1:13" ht="289" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="6">
+        <v>400</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="37">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I4" s="4">
+        <f>46000000*(100*2)/1000000000</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="32">
+        <v>385</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="38">
+        <v>0</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="I5" s="35">
+        <f>9160000/2.5*(150*2)/1000000000</f>
+        <v>1.0992</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:13" ht="323" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="6">
+        <v>370</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="39">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I6" s="6">
+        <f>20000000*(82.5*2)/1000000000</f>
+        <v>3.3</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="255" x14ac:dyDescent="0.2">
+      <c r="A7" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="32">
+        <v>292</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="G3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="17.100000000000001">
-      <c r="B4" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="D4" s="21">
-        <v>99.578999999999994</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="17.100000000000001">
-      <c r="B5" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="D5" s="21">
-        <v>99.578999999999994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="17.100000000000001">
-      <c r="A6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D6" s="21">
-        <v>99.950999999999993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="17.100000000000001">
-      <c r="B7" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" s="21">
-        <v>92.688999999999993</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.100000000000001">
-      <c r="B8" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="D8" s="21">
-        <v>92.738</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.100000000000001">
-      <c r="A9" t="s">
-        <v>296</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="21">
-        <v>99.91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.100000000000001">
-      <c r="A10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="D10" s="21">
-        <v>98.506</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.100000000000001">
-      <c r="B11" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="D11" s="21">
-        <v>97.63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.100000000000001">
-      <c r="B12" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="D12" s="21">
-        <v>92.272000000000006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.100000000000001">
-      <c r="B13" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D13" s="21">
-        <v>91.841999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.100000000000001">
-      <c r="B14" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D14" s="21">
-        <v>91.087000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17.100000000000001">
-      <c r="B15" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D15" s="21">
-        <v>90.828999999999994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.100000000000001">
-      <c r="B16" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="D16" s="21">
-        <v>96.856999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.100000000000001">
-      <c r="B17" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="D17" s="21">
-        <v>92.022999999999996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17.100000000000001">
-      <c r="B18" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D18" s="21">
-        <v>91.578999999999994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="17.100000000000001">
-      <c r="B19" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D19" s="21">
-        <v>90.828999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="17.100000000000001">
-      <c r="B20" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D20" s="21">
-        <v>90.478999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="17.100000000000001">
-      <c r="B21" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="D21" s="21">
-        <v>91.757000000000005</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="17.100000000000001">
-      <c r="B22" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D22" s="21">
-        <v>91.477999999999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="17.100000000000001">
-      <c r="B23" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D23" s="21">
-        <v>90.674999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="17.100000000000001">
-      <c r="B24" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D24" s="21">
-        <v>90.366</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17.100000000000001">
-      <c r="B25" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D25" s="21">
-        <v>94.632000000000005</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="17.100000000000001">
-      <c r="B26" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D26" s="21">
-        <v>92.89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="17.100000000000001">
-      <c r="B27" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D27" s="21">
-        <v>92.588999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="17.100000000000001">
-      <c r="B28" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D28" s="21">
-        <v>92.841999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="17.100000000000001">
-      <c r="B29" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D29" s="21">
-        <v>92.421000000000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17.100000000000001">
-      <c r="B30" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="D30" s="21">
-        <v>98.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>307</v>
-      </c>
+      <c r="D7" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="40">
+        <v>0.318</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="I7" s="36">
+        <f>34100000*(75*2)/1000000000</f>
+        <v>5.1150000000000002</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>331</v>
+      </c>
+      <c r="L7" s="41"/>
+    </row>
+    <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="6">
+        <v>249</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="39">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="32">
+        <v>249</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>335</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="K9" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="L9" s="41"/>
+    </row>
+    <row r="10" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="6">
+        <v>233</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="39">
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A11" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="32">
+        <v>232</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>341</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" s="41"/>
+    </row>
+    <row r="12" spans="1:13" ht="340" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="6">
+        <v>168</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="43">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="32">
+        <v>168</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="42">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="L13" s="41"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="6">
+        <v>156</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="44">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A15" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="32">
+        <v>140</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>351</v>
+      </c>
+      <c r="K15" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="L15" s="35" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="6">
+        <v>128</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="44">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="I16" s="6">
+        <f>((60496561+60162577)/2)*200/1000000000</f>
+        <v>12.065913800000001</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+      <c r="A17" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="32">
+        <v>111</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="42">
+        <v>0.189</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="I17" s="46">
+        <f>26202286*150*2/1000000000</f>
+        <v>7.8606857999999997</v>
+      </c>
+      <c r="J17" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="K17" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="L17" s="47"/>
+      <c r="M17" s="48"/>
+    </row>
+    <row r="18" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="6">
+        <v>110</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="44">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A19" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="32">
+        <v>97</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="42">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>365</v>
+      </c>
+      <c r="I19" s="36">
+        <f>30000000*200/1000000000</f>
+        <v>6</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="6">
+        <v>97</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="43">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L20" s="50"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+      <c r="A21" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="32">
+        <v>92</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="I21" s="36">
+        <f>10900000*200/1000000000</f>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="J21" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="K21" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="L21" s="41"/>
+    </row>
+    <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="6">
+        <v>69</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="43">
+        <v>0.377</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A23" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="32">
+        <v>63</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="42">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="I23" s="35">
+        <f>15000000*100*2/1000000000</f>
+        <v>3</v>
+      </c>
+      <c r="J23" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="K23" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="L23" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A24" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="6">
+        <v>59</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="44">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A25" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="32">
+        <v>58</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="51">
+        <v>0</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="I25" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="6">
+        <v>55</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="44">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+      <c r="A27" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="32">
+        <v>52</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="G27" s="51">
+        <v>0</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>387</v>
+      </c>
+      <c r="I27" s="47">
+        <f>3850*1000000/1000000000</f>
+        <v>3.85</v>
+      </c>
+      <c r="J27" s="47" t="s">
+        <v>388</v>
+      </c>
+      <c r="K27" s="35" t="s">
+        <v>389</v>
+      </c>
+      <c r="L27" s="54"/>
+      <c r="M27" s="55"/>
+    </row>
+    <row r="28" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="6">
+        <v>51</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G28" s="56">
+        <v>0</v>
+      </c>
+      <c r="H28" s="57" t="s">
+        <v>390</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>362</v>
+      </c>
+      <c r="K28" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="L28" s="59" t="s">
+        <v>373</v>
+      </c>
+      <c r="M28" s="57"/>
+    </row>
+    <row r="29" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A29" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="32">
+        <v>50</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="51">
+        <v>0</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="I29" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="36" t="s">
+        <v>393</v>
+      </c>
+      <c r="K29" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="L29" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4608,17 +6172,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2691488b-3dd8-43fd-b5f5-646823e2c29f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a046886a-180d-4fc1-a6d0-e96a37e96865" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F6E53307F14164BBA3202DD555B66FC" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fb955171c2d2d6f6906c6f16fff743d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2691488b-3dd8-43fd-b5f5-646823e2c29f" xmlns:ns3="a046886a-180d-4fc1-a6d0-e96a37e96865" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c487210bddde17f76e42b1e6eb287d30" ns2:_="" ns3:_="">
     <xsd:import namespace="2691488b-3dd8-43fd-b5f5-646823e2c29f"/>
@@ -4819,14 +6372,51 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2691488b-3dd8-43fd-b5f5-646823e2c29f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a046886a-180d-4fc1-a6d0-e96a37e96865" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B9679A-D51F-447F-93C1-A19C5B2235EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B9679A-D51F-447F-93C1-A19C5B2235EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D21B7F-17C7-44E2-BB80-2FF62049EBCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{208B3D5A-67FF-4BB3-901D-54C3C2E1758B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2691488b-3dd8-43fd-b5f5-646823e2c29f"/>
+    <ds:schemaRef ds:uri="a046886a-180d-4fc1-a6d0-e96a37e96865"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{208B3D5A-67FF-4BB3-901D-54C3C2E1758B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D21B7F-17C7-44E2-BB80-2FF62049EBCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2691488b-3dd8-43fd-b5f5-646823e2c29f"/>
+    <ds:schemaRef ds:uri="a046886a-180d-4fc1-a6d0-e96a37e96865"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SupplementaryTables/ssrm_suppTables.xlsx
+++ b/SupplementaryTables/ssrm_suppTables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ehd5113/human-gut-ssrm-capscan/SupplementaryTables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CA07A2-6D62-144C-9B21-489D72FBCA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6585364D-A3F5-FD45-9632-191683E8420A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29100" windowHeight="16840" activeTab="3" xr2:uid="{C171AF22-812F-0C42-B48C-B2ABBD8475A5}"/>
+    <workbookView xWindow="2620" yWindow="760" windowWidth="29100" windowHeight="16840" activeTab="3" xr2:uid="{C171AF22-812F-0C42-B48C-B2ABBD8475A5}"/>
   </bookViews>
   <sheets>
     <sheet name="SuppTable1" sheetId="4" r:id="rId1"/>
@@ -317,9 +317,6 @@
     <t>InfantGut: Dynamics and Stabilization of the Human Gut Microbiome during the First Year of Life</t>
   </si>
   <si>
-    <t>Denmark or Sweden</t>
-  </si>
-  <si>
     <t>PRJNA301903</t>
   </si>
   <si>
@@ -1057,12 +1054,6 @@
     <t>Sequencing depth notes</t>
   </si>
   <si>
-    <t>Reads to Gnt calculation</t>
-  </si>
-  <si>
-    <t>Depth in Gnt, pre- or post-"QC" (trim, human-reads removal, etc.)</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
@@ -1323,6 +1314,15 @@
   </si>
   <si>
     <t>https://doi.org/10.7554/eLife.05477</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Reads to Gigabases calculation</t>
+  </si>
+  <si>
+    <t>Depth in Gb, pre- or post-"QC" (trim, human-reads removal, etc.)</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1563,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1606,13 +1606,6 @@
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1704,6 +1697,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2459,42 +2462,42 @@
       <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="57">
         <v>44593</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="55" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="59">
         <v>13329</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="59">
         <v>13329</v>
       </c>
       <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
       <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="57">
         <v>44593</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -2503,186 +2506,186 @@
       <c r="D7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="59">
         <v>51890</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="59">
         <v>42314</v>
       </c>
       <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22" t="s">
+      <c r="A8" s="56"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
       <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
       <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
       <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
       <c r="D11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
       <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
       <c r="G12" s="19"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
       <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
       <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
       <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
       <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
       <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
       <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
       <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
       <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
       <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
       <c r="D22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="57">
         <v>44593</v>
       </c>
       <c r="C23" s="17" t="s">
@@ -2691,98 +2694,98 @@
       <c r="D23" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="59">
         <v>24738</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="59">
         <v>19367</v>
       </c>
       <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="22" t="s">
+      <c r="A24" s="56"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
       <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
       <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="56"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="56"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
       <c r="D27" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
       <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
       <c r="D28" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
       <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
+      <c r="A29" s="56"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
       <c r="D29" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
       <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
       <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="57">
         <v>44593</v>
       </c>
       <c r="C31" s="17" t="s">
@@ -2791,43 +2794,43 @@
       <c r="D31" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="55">
         <v>462</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="55">
         <v>255</v>
       </c>
       <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="22" t="s">
+      <c r="A32" s="56"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
       <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
+      <c r="A33" s="56"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
       <c r="D33" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
       <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="57">
         <v>44594</v>
       </c>
       <c r="C34" s="17" t="s">
@@ -2836,43 +2839,43 @@
       <c r="D34" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="55">
         <v>173</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="55">
         <v>115</v>
       </c>
       <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="22" t="s">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
       <c r="G35" s="17"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
+      <c r="A36" s="56"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
       <c r="D36" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
       <c r="G36" s="17"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="57">
         <v>44593</v>
       </c>
       <c r="C37" s="17" t="s">
@@ -2881,87 +2884,87 @@
       <c r="D37" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="59">
         <v>6264</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="59">
         <v>5481</v>
       </c>
       <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="22" t="s">
+      <c r="A38" s="56"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
       <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
       <c r="D39" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
       <c r="G39" s="19"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
+      <c r="A40" s="56"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
       <c r="D40" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
       <c r="G40" s="19"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
+      <c r="A41" s="56"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
       <c r="D41" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
       <c r="G41" s="19"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
       <c r="D42" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
       <c r="G42" s="19"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
       <c r="G43" s="19"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="57">
         <v>44593</v>
       </c>
       <c r="C44" s="17" t="s">
@@ -2970,120 +2973,120 @@
       <c r="D44" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="59">
         <v>4620</v>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="59">
         <v>4152</v>
       </c>
       <c r="G44" s="19"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="22" t="s">
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
       <c r="G45" s="19"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
       <c r="D46" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
       <c r="G46" s="19"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
       <c r="D47" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
       <c r="G47" s="19"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
       <c r="D48" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
       <c r="G48" s="19"/>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="23"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
       <c r="D49" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
       <c r="G49" s="19"/>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
       <c r="D50" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
       <c r="G50" s="19"/>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="23"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
       <c r="D51" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
       <c r="G51" s="19"/>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="23"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
       <c r="D52" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
       <c r="G52" s="19"/>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="23"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
+      <c r="A53" s="56"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
       <c r="D53" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
       <c r="G53" s="19"/>
     </row>
     <row r="54" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="57">
         <v>44593</v>
       </c>
       <c r="C54" s="17" t="s">
@@ -3092,43 +3095,43 @@
       <c r="D54" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="55">
         <v>796</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="55">
         <v>637</v>
       </c>
       <c r="G54" s="17"/>
     </row>
     <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="22" t="s">
+      <c r="A55" s="56"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="56"/>
       <c r="G55" s="17"/>
     </row>
     <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
       <c r="D56" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
       <c r="G56" s="17"/>
     </row>
     <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B57" s="57">
         <v>44594</v>
       </c>
       <c r="C57" s="17" t="s">
@@ -3137,34 +3140,34 @@
       <c r="D57" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="55">
         <v>58</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="55">
         <v>58</v>
       </c>
       <c r="G57" s="17"/>
     </row>
     <row r="58" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="56"/>
+      <c r="B58" s="56"/>
       <c r="C58" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
       <c r="G58" s="17"/>
     </row>
     <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.2">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
       <c r="E59" s="19">
         <f>SUM(E4:E56)</f>
         <v>111914</v>
@@ -3179,51 +3182,51 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A7:A22"/>
+    <mergeCell ref="B7:B22"/>
+    <mergeCell ref="E7:E22"/>
+    <mergeCell ref="F7:F22"/>
+    <mergeCell ref="C8:C22"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="E23:E30"/>
+    <mergeCell ref="F23:F30"/>
+    <mergeCell ref="C24:C30"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="E37:E43"/>
+    <mergeCell ref="F37:F43"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="A44:A53"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="E44:E53"/>
+    <mergeCell ref="F44:F53"/>
+    <mergeCell ref="C45:C53"/>
     <mergeCell ref="A57:A58"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="E44:E53"/>
-    <mergeCell ref="F44:F53"/>
-    <mergeCell ref="C45:C53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="A37:A43"/>
-    <mergeCell ref="B37:B43"/>
-    <mergeCell ref="E37:E43"/>
-    <mergeCell ref="F37:F43"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="E23:E30"/>
-    <mergeCell ref="F23:F30"/>
-    <mergeCell ref="C24:C30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A7:A22"/>
-    <mergeCell ref="B7:B22"/>
-    <mergeCell ref="E7:E22"/>
-    <mergeCell ref="F7:F22"/>
-    <mergeCell ref="C8:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3242,27 +3245,27 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" t="s">
         <v>280</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>281</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>282</v>
-      </c>
-      <c r="D1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="C2" s="21" t="s">
         <v>285</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>286</v>
       </c>
       <c r="D2" s="21">
         <v>99.844999999999999</v>
@@ -3270,27 +3273,27 @@
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="C3" s="21" t="s">
         <v>288</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>289</v>
       </c>
       <c r="D3" s="21">
         <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D4" s="21">
         <v>99.578999999999994</v>
@@ -3298,10 +3301,10 @@
     </row>
     <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D5" s="21">
         <v>99.578999999999994</v>
@@ -3309,13 +3312,13 @@
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="C6" s="21" t="s">
         <v>293</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>294</v>
       </c>
       <c r="D6" s="21">
         <v>99.950999999999993</v>
@@ -3323,10 +3326,10 @@
     </row>
     <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D7" s="21">
         <v>92.688999999999993</v>
@@ -3334,10 +3337,10 @@
     </row>
     <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>294</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>295</v>
       </c>
       <c r="D8" s="21">
         <v>92.738</v>
@@ -3345,13 +3348,13 @@
     </row>
     <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="C9" s="21" t="s">
         <v>297</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>298</v>
       </c>
       <c r="D9" s="21">
         <v>99.91</v>
@@ -3359,13 +3362,13 @@
     </row>
     <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="21" t="s">
         <v>300</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>301</v>
       </c>
       <c r="D10" s="21">
         <v>98.506</v>
@@ -3373,10 +3376,10 @@
     </row>
     <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D11" s="21">
         <v>97.63</v>
@@ -3384,10 +3387,10 @@
     </row>
     <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D12" s="21">
         <v>92.272000000000006</v>
@@ -3395,10 +3398,10 @@
     </row>
     <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D13" s="21">
         <v>91.841999999999999</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D14" s="21">
         <v>91.087000000000003</v>
@@ -3417,10 +3420,10 @@
     </row>
     <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B15" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D15" s="21">
         <v>90.828999999999994</v>
@@ -3428,10 +3431,10 @@
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.25">
       <c r="B16" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>301</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>302</v>
       </c>
       <c r="D16" s="21">
         <v>96.856999999999999</v>
@@ -3439,10 +3442,10 @@
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D17" s="21">
         <v>92.022999999999996</v>
@@ -3450,10 +3453,10 @@
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B18" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D18" s="21">
         <v>91.578999999999994</v>
@@ -3461,10 +3464,10 @@
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B19" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D19" s="21">
         <v>90.828999999999994</v>
@@ -3472,10 +3475,10 @@
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D20" s="21">
         <v>90.478999999999999</v>
@@ -3483,10 +3486,10 @@
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B21" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>302</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>303</v>
       </c>
       <c r="D21" s="21">
         <v>91.757000000000005</v>
@@ -3494,10 +3497,10 @@
     </row>
     <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B22" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D22" s="21">
         <v>91.477999999999994</v>
@@ -3505,10 +3508,10 @@
     </row>
     <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B23" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D23" s="21">
         <v>90.674999999999997</v>
@@ -3516,10 +3519,10 @@
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B24" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D24" s="21">
         <v>90.366</v>
@@ -3527,10 +3530,10 @@
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B25" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>303</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>304</v>
       </c>
       <c r="D25" s="21">
         <v>94.632000000000005</v>
@@ -3538,10 +3541,10 @@
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B26" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D26" s="21">
         <v>92.89</v>
@@ -3549,10 +3552,10 @@
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B27" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D27" s="21">
         <v>92.588999999999999</v>
@@ -3560,10 +3563,10 @@
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>304</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>305</v>
       </c>
       <c r="D28" s="21">
         <v>92.841999999999999</v>
@@ -3571,10 +3574,10 @@
     </row>
     <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B29" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D29" s="21">
         <v>92.421000000000006</v>
@@ -3582,10 +3585,10 @@
     </row>
     <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.25">
       <c r="B30" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>305</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>306</v>
       </c>
       <c r="D30" s="21">
         <v>98.2</v>
@@ -3593,7 +3596,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3687,8 +3690,8 @@
       <c r="D4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>91</v>
+      <c r="E4" s="60" t="s">
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -3696,13 +3699,13 @@
     </row>
     <row r="5" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3">
         <v>385</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>86</v>
@@ -3711,144 +3714,144 @@
         <v>82</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3">
         <v>370</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3">
         <v>292</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3">
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3">
         <v>233</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="3">
         <v>232</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="3">
         <v>168</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>83</v>
@@ -3856,93 +3859,93 @@
     </row>
     <row r="13" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13" s="3">
         <v>168</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="3">
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="3">
         <v>140</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" s="3">
         <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3">
         <v>111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>81</v>
@@ -3956,13 +3959,13 @@
     </row>
     <row r="18" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3">
         <v>110</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>81</v>
@@ -3971,84 +3974,84 @@
         <v>82</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3">
         <v>97</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3">
         <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>92</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3">
         <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
@@ -4056,13 +4059,13 @@
     </row>
     <row r="23" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3">
         <v>63</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>81</v>
@@ -4076,39 +4079,39 @@
     </row>
     <row r="24" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3">
         <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>83</v>
@@ -4116,53 +4119,53 @@
     </row>
     <row r="26" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B26" s="3">
         <v>55</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B27" s="3">
         <v>52</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" s="3">
         <v>51</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>81</v>
@@ -4171,18 +4174,18 @@
         <v>82</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" s="3">
         <v>50</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>86</v>
@@ -4191,44 +4194,44 @@
         <v>82</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3">
         <v>49</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B31" s="3">
         <v>38</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>83</v>
@@ -4236,13 +4239,13 @@
     </row>
     <row r="32" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3">
         <v>37</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>81</v>
@@ -4256,13 +4259,13 @@
     </row>
     <row r="33" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B33" s="3">
         <v>37</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>86</v>
@@ -4271,18 +4274,18 @@
         <v>82</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3">
         <v>36</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>86</v>
@@ -4291,104 +4294,104 @@
         <v>82</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B35" s="3">
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B36" s="3">
         <v>29</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" s="3">
         <v>29</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B38" s="3">
         <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" s="3">
         <v>24</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>195</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>83</v>
@@ -4396,33 +4399,33 @@
     </row>
     <row r="40" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B40" s="3">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" s="3">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>81</v>
@@ -4431,24 +4434,24 @@
         <v>82</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B42" s="3">
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>204</v>
-      </c>
       <c r="E42" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>83</v>
@@ -4456,13 +4459,13 @@
     </row>
     <row r="43" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B43" s="3">
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>81</v>
@@ -4476,33 +4479,33 @@
     </row>
     <row r="44" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B45" s="3">
         <v>11</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>86</v>
@@ -4511,38 +4514,38 @@
         <v>82</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B46" s="3">
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B47" s="3">
         <v>10</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>81</v>
@@ -4551,24 +4554,24 @@
         <v>82</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>83</v>
@@ -4576,53 +4579,53 @@
     </row>
     <row r="49" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B49" s="3">
         <v>9</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B50" s="3">
         <v>9</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B51" s="3">
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>81</v>
@@ -4636,79 +4639,79 @@
     </row>
     <row r="52" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B52" s="3">
         <v>9</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B53" s="3">
         <v>8</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3">
         <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3">
         <v>6</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>83</v>
@@ -4716,19 +4719,19 @@
     </row>
     <row r="56" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B56" s="3">
         <v>6</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>83</v>
@@ -4736,19 +4739,19 @@
     </row>
     <row r="57" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3">
         <v>4</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>83</v>
@@ -4756,39 +4759,39 @@
     </row>
     <row r="58" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3">
         <v>4</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="F58" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B59" s="3">
         <v>3</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>83</v>
@@ -4796,33 +4799,33 @@
     </row>
     <row r="60" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B60" s="3">
         <v>3</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B61" s="3">
         <v>2</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>81</v>
@@ -4836,13 +4839,13 @@
     </row>
     <row r="62" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3">
         <v>2</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>81</v>
@@ -4856,13 +4859,13 @@
     </row>
     <row r="63" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B63" s="3">
         <v>2</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>86</v>
@@ -4871,24 +4874,24 @@
         <v>82</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B64" s="3">
         <v>2</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>83</v>
@@ -4896,13 +4899,13 @@
     </row>
     <row r="65" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B65" s="3">
         <v>2</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>81</v>
@@ -4911,38 +4914,38 @@
         <v>82</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B66" s="3">
         <v>2</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E66" s="6" t="s">
+      <c r="F66" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>86</v>
@@ -4951,24 +4954,24 @@
         <v>82</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>83</v>
@@ -4976,19 +4979,19 @@
     </row>
     <row r="69" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B69" s="3">
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>83</v>
@@ -4996,19 +4999,19 @@
     </row>
     <row r="70" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B70" s="3">
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>83</v>
@@ -5016,19 +5019,19 @@
     </row>
     <row r="71" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>81</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>83</v>
@@ -5036,22 +5039,22 @@
     </row>
     <row r="72" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B72" s="3">
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -5079,41 +5082,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="I1" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="K1" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="L1" s="25" t="s">
         <v>310</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>311</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="L1" s="30" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="119" x14ac:dyDescent="0.2">
@@ -5135,58 +5138,58 @@
       <c r="F2" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="26">
         <v>9.4E-2</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="27">
+        <v>737</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="29">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="H3" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I3" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K3" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="32">
-        <v>737</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="34">
-        <v>1.6299999999999999E-2</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="I3" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J3" s="36" t="s">
-        <v>318</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>319</v>
-      </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:13" ht="289" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -5199,521 +5202,521 @@
         <v>90</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>91</v>
+        <v>392</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="37">
+      <c r="G4" s="32">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I4" s="4">
         <f>46000000*(100*2)/1000000000</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:13" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="27">
+        <v>385</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="32">
-        <v>385</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="D5" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="38">
+      <c r="G5" s="33">
         <v>0</v>
       </c>
-      <c r="H5" s="35" t="s">
-        <v>323</v>
-      </c>
-      <c r="I5" s="35">
+      <c r="H5" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="I5" s="30">
         <f>9160000/2.5*(150*2)/1000000000</f>
         <v>1.0992</v>
       </c>
-      <c r="J5" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="L5" s="36"/>
+      <c r="J5" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:13" ht="323" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="6">
         <v>370</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="39">
+      <c r="G6" s="34">
         <v>0.35399999999999998</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I6" s="6">
         <f>20000000*(82.5*2)/1000000000</f>
         <v>3.3</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="255" x14ac:dyDescent="0.2">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="27">
+        <v>292</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="32">
-        <v>292</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="D7" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="F7" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="40">
+      <c r="G7" s="35">
         <v>0.318</v>
       </c>
-      <c r="H7" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="I7" s="36">
+      <c r="H7" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="I7" s="31">
         <f>34100000*(75*2)/1000000000</f>
         <v>5.1150000000000002</v>
       </c>
-      <c r="J7" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="K7" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="L7" s="41"/>
+      <c r="J7" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="L7" s="36"/>
     </row>
     <row r="8" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="6">
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="34">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="39">
-        <v>0.52200000000000002</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="B9" s="27">
+        <v>249</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="35">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J8" s="6" t="s">
+      <c r="I9" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J9" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K9" s="30" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A9" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="32">
-        <v>249</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="40">
-        <v>0.58199999999999996</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>335</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="K9" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="L9" s="41"/>
+      <c r="L9" s="36"/>
     </row>
     <row r="10" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="6">
         <v>233</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A11" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="G10" s="39">
-        <v>0.15</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="B11" s="27">
+        <v>232</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="37">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="H11" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="I11" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="K11" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="32">
-        <v>232</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" s="42">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="K11" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="L11" s="41"/>
+      <c r="L11" s="36"/>
     </row>
     <row r="12" spans="1:13" ht="340" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="6">
         <v>168</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="38">
         <v>0.29199999999999998</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="27">
+        <v>168</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="32">
-        <v>168</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="G13" s="42">
+      <c r="D13" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="37">
         <v>0.54800000000000004</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="K13" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="L13" s="41"/>
+      <c r="H13" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="L13" s="36"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="6">
         <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="39">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A15" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="44">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J14" s="6" t="s">
+      <c r="B15" s="27">
+        <v>140</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="37">
+        <v>0.8</v>
+      </c>
+      <c r="H15" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="I15" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="K15" s="30" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="32">
-        <v>140</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="42">
-        <v>0.8</v>
-      </c>
-      <c r="H15" s="35" t="s">
+      <c r="L15" s="30" t="s">
         <v>350</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="K15" s="35" t="s">
-        <v>352</v>
-      </c>
-      <c r="L15" s="35" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" s="6">
         <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>81</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="44">
+        <v>122</v>
+      </c>
+      <c r="G16" s="39">
         <v>0</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I16" s="6">
         <f>((60496561+60162577)/2)*200/1000000000</f>
         <v>12.065913800000001</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+      <c r="A17" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="27">
+        <v>111</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="37">
+        <v>0.189</v>
+      </c>
+      <c r="H17" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="153" x14ac:dyDescent="0.2">
-      <c r="A17" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" s="32">
-        <v>111</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="42">
-        <v>0.189</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>358</v>
-      </c>
-      <c r="I17" s="46">
+      <c r="I17" s="41">
         <f>26202286*150*2/1000000000</f>
         <v>7.8606857999999997</v>
       </c>
-      <c r="J17" s="46" t="s">
-        <v>359</v>
-      </c>
-      <c r="K17" s="35" t="s">
-        <v>360</v>
-      </c>
-      <c r="L17" s="47"/>
-      <c r="M17" s="48"/>
+      <c r="J17" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="L17" s="42"/>
+      <c r="M17" s="43"/>
     </row>
     <row r="18" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B18" s="6">
         <v>110</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>81</v>
@@ -5722,375 +5725,375 @@
         <v>82</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G18" s="44">
+        <v>122</v>
+      </c>
+      <c r="G18" s="39">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="L18" s="44" t="s">
         <v>361</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A19" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="27">
+        <v>97</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="37">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="H19" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="L18" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A19" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" s="32">
-        <v>97</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="G19" s="42">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="I19" s="36">
+      <c r="I19" s="31">
         <f>30000000*200/1000000000</f>
         <v>6</v>
       </c>
-      <c r="J19" s="36" t="s">
-        <v>366</v>
-      </c>
-      <c r="K19" s="35" t="s">
-        <v>367</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>368</v>
+      <c r="J19" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="L19" s="30" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" s="6">
         <v>97</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="38">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L20" s="45"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+      <c r="A21" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="43">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="L20" s="50"/>
-      <c r="M20" s="6"/>
-    </row>
-    <row r="21" spans="1:13" ht="136" x14ac:dyDescent="0.2">
-      <c r="A21" s="32" t="s">
+      <c r="B21" s="27">
+        <v>92</v>
+      </c>
+      <c r="C21" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="32">
-        <v>92</v>
-      </c>
-      <c r="C21" s="33" t="s">
+      <c r="D21" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="51">
+      <c r="F21" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="46">
         <v>0</v>
       </c>
-      <c r="H21" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="I21" s="36">
+      <c r="H21" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="I21" s="31">
         <f>10900000*200/1000000000</f>
         <v>2.1800000000000002</v>
       </c>
-      <c r="J21" s="36" t="s">
-        <v>370</v>
-      </c>
-      <c r="K21" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="L21" s="41"/>
+      <c r="J21" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="L21" s="36"/>
     </row>
     <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B22" s="6">
         <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="38">
         <v>0.377</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="27">
+        <v>63</v>
+      </c>
+      <c r="C23" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="32">
-        <v>63</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="32" t="s">
+      <c r="D23" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="37">
         <v>0.38100000000000001</v>
       </c>
-      <c r="H23" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="I23" s="35">
+      <c r="H23" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="I23" s="30">
         <f>15000000*100*2/1000000000</f>
         <v>3</v>
       </c>
-      <c r="J23" s="35" t="s">
-        <v>375</v>
-      </c>
-      <c r="K23" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="L23" s="35" t="s">
-        <v>377</v>
+      <c r="J23" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="L23" s="30" t="s">
+        <v>374</v>
       </c>
       <c r="M23" s="4"/>
     </row>
     <row r="24" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A24" s="52" t="s">
-        <v>146</v>
+      <c r="A24" s="47" t="s">
+        <v>145</v>
       </c>
       <c r="B24" s="6">
         <v>59</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="39">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A25" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="44">
+      <c r="B25" s="27">
+        <v>58</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="46">
         <v>0</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J24" s="6" t="s">
+      <c r="H25" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="I25" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A25" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="32">
-        <v>58</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="51">
-        <v>0</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>382</v>
-      </c>
-      <c r="I25" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="J25" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" s="35" t="s">
-        <v>383</v>
-      </c>
-      <c r="L25" s="41"/>
+      <c r="L25" s="36"/>
     </row>
     <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B26" s="6">
         <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="39">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+      <c r="A27" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="G26" s="44">
+      <c r="B27" s="27">
+        <v>52</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="G27" s="46">
         <v>0</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="48" t="s">
         <v>384</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="221" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" s="32">
-        <v>52</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27" s="51">
-        <v>0</v>
-      </c>
-      <c r="H27" s="53" t="s">
-        <v>387</v>
-      </c>
-      <c r="I27" s="47">
+      <c r="I27" s="42">
         <f>3850*1000000/1000000000</f>
         <v>3.85</v>
       </c>
-      <c r="J27" s="47" t="s">
-        <v>388</v>
-      </c>
-      <c r="K27" s="35" t="s">
-        <v>389</v>
-      </c>
-      <c r="L27" s="54"/>
-      <c r="M27" s="55"/>
+      <c r="J27" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="L27" s="49"/>
+      <c r="M27" s="50"/>
     </row>
     <row r="28" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" s="6">
         <v>51</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>81</v>
@@ -6099,63 +6102,63 @@
         <v>82</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="51">
+        <v>0</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>387</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="52" t="s">
+        <v>359</v>
+      </c>
+      <c r="K28" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="L28" s="54" t="s">
+        <v>370</v>
+      </c>
+      <c r="M28" s="52"/>
+    </row>
+    <row r="29" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A29" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="56">
+      <c r="B29" s="27">
+        <v>50</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="46">
         <v>0</v>
       </c>
-      <c r="H28" s="57" t="s">
+      <c r="H29" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="I29" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="I28" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="J28" s="57" t="s">
-        <v>362</v>
-      </c>
-      <c r="K28" s="58" t="s">
+      <c r="K29" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="L28" s="59" t="s">
-        <v>373</v>
-      </c>
-      <c r="M28" s="57"/>
-    </row>
-    <row r="29" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A29" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="B29" s="32">
-        <v>50</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="G29" s="51">
-        <v>0</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>392</v>
-      </c>
-      <c r="I29" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="J29" s="36" t="s">
-        <v>393</v>
-      </c>
-      <c r="K29" s="35" t="s">
-        <v>394</v>
-      </c>
-      <c r="L29" s="41"/>
+      <c r="L29" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6163,12 +6166,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2691488b-3dd8-43fd-b5f5-646823e2c29f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a046886a-180d-4fc1-a6d0-e96a37e96865" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6373,20 +6378,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2691488b-3dd8-43fd-b5f5-646823e2c29f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a046886a-180d-4fc1-a6d0-e96a37e96865" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B9679A-D51F-447F-93C1-A19C5B2235EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D21B7F-17C7-44E2-BB80-2FF62049EBCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2691488b-3dd8-43fd-b5f5-646823e2c29f"/>
+    <ds:schemaRef ds:uri="a046886a-180d-4fc1-a6d0-e96a37e96865"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6411,12 +6417,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D21B7F-17C7-44E2-BB80-2FF62049EBCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B9679A-D51F-447F-93C1-A19C5B2235EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2691488b-3dd8-43fd-b5f5-646823e2c29f"/>
-    <ds:schemaRef ds:uri="a046886a-180d-4fc1-a6d0-e96a37e96865"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>